--- a/data/raw/benv_exports/leishmaniosi_2026_italia.xlsx
+++ b/data/raw/benv_exports/leishmaniosi_2026_italia.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>85169</v>
+        <v>85709</v>
       </c>
       <c r="B2" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -423,13 +423,13 @@
         <v>E</v>
       </c>
       <c r="D2" t="str">
-        <v>16/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="E2" t="str">
-        <v>16/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="F2" t="str">
-        <v>16/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -438,7 +438,7 @@
         <v>CANE</v>
       </c>
       <c r="I2" t="str">
-        <v>GROSSETO</v>
+        <v>GAVORRANO</v>
       </c>
       <c r="J2" t="str">
         <v>GR</v>
@@ -449,7 +449,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>85202</v>
+        <v>85203</v>
       </c>
       <c r="B3" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
@@ -484,7 +484,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>85171</v>
+        <v>85169</v>
       </c>
       <c r="B4" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -508,7 +508,7 @@
         <v>CANE</v>
       </c>
       <c r="I4" t="str">
-        <v>CAMPAGNATICO</v>
+        <v>GROSSETO</v>
       </c>
       <c r="J4" t="str">
         <v>GR</v>
@@ -519,22 +519,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>85115</v>
+        <v>85202</v>
       </c>
       <c r="B5" t="str">
-        <v>FOCOLAIO CLINICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C5" t="str">
         <v>E</v>
       </c>
       <c r="D5" t="str">
-        <v>16/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="E5" t="str">
-        <v>16/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="F5" t="str">
-        <v>16/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -554,22 +554,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>85197</v>
+        <v>85658</v>
       </c>
       <c r="B6" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C6" t="str">
         <v>E</v>
       </c>
       <c r="D6" t="str">
-        <v>19/06/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="E6" t="str">
-        <v>19/06/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="F6" t="str">
-        <v>19/06/2026</v>
+        <v>16/07/2026</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -578,7 +578,7 @@
         <v>CANE</v>
       </c>
       <c r="I6" t="str">
-        <v>GROSSETO</v>
+        <v>SCANSANO</v>
       </c>
       <c r="J6" t="str">
         <v>GR</v>
@@ -589,22 +589,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>85203</v>
+        <v>85171</v>
       </c>
       <c r="B7" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C7" t="str">
         <v>E</v>
       </c>
       <c r="D7" t="str">
-        <v>19/06/2026</v>
+        <v>16/06/2026</v>
       </c>
       <c r="E7" t="str">
-        <v>19/06/2026</v>
+        <v>16/06/2026</v>
       </c>
       <c r="F7" t="str">
-        <v>19/06/2026</v>
+        <v>16/06/2026</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -613,7 +613,7 @@
         <v>CANE</v>
       </c>
       <c r="I7" t="str">
-        <v>GROSSETO</v>
+        <v>CAMPAGNATICO</v>
       </c>
       <c r="J7" t="str">
         <v>GR</v>
@@ -624,22 +624,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>84096</v>
+        <v>85655</v>
       </c>
       <c r="B8" t="str">
         <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C8" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D8" t="str">
-        <v>27/03/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="E8" t="str">
-        <v>20/03/2026</v>
+        <v>01/06/2026</v>
       </c>
       <c r="F8" t="str">
-        <v>-</v>
+        <v>16/07/2026</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -648,33 +648,33 @@
         <v>CANE</v>
       </c>
       <c r="I8" t="str">
-        <v>BATTAGLIA TERME</v>
+        <v>GROSSETO</v>
       </c>
       <c r="J8" t="str">
-        <v>PD</v>
+        <v>GR</v>
       </c>
       <c r="K8" t="str">
-        <v>VENETO</v>
+        <v>TOSCANA</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>84882</v>
+        <v>85823</v>
       </c>
       <c r="B9" t="str">
-        <v>POSITIVITA' DIAGNOSTICA</v>
+        <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C9" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D9" t="str">
-        <v>17/04/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="E9" t="str">
-        <v>15/04/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="F9" t="str">
-        <v>-</v>
+        <v>24/07/2026</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -683,33 +683,33 @@
         <v>CANE</v>
       </c>
       <c r="I9" t="str">
-        <v>MALO</v>
+        <v>GROSSETO</v>
       </c>
       <c r="J9" t="str">
-        <v>VI</v>
+        <v>GR</v>
       </c>
       <c r="K9" t="str">
-        <v>VENETO</v>
+        <v>TOSCANA</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>83740</v>
+        <v>85824</v>
       </c>
       <c r="B10" t="str">
         <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C10" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D10" t="str">
-        <v>14/02/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="E10" t="str">
-        <v>14/02/2026</v>
+        <v>16/07/2026</v>
       </c>
       <c r="F10" t="str">
-        <v>-</v>
+        <v>24/07/2026</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -718,33 +718,33 @@
         <v>CANE</v>
       </c>
       <c r="I10" t="str">
-        <v>VALDOBBIADENE</v>
+        <v>GROSSETO</v>
       </c>
       <c r="J10" t="str">
-        <v>TV</v>
+        <v>GR</v>
       </c>
       <c r="K10" t="str">
-        <v>VENETO</v>
+        <v>TOSCANA</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>85011</v>
+        <v>85115</v>
       </c>
       <c r="B11" t="str">
         <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C11" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D11" t="str">
-        <v>15/05/2026</v>
+        <v>16/06/2026</v>
       </c>
       <c r="E11" t="str">
-        <v>14/05/2026</v>
+        <v>16/06/2026</v>
       </c>
       <c r="F11" t="str">
-        <v>-</v>
+        <v>16/06/2026</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -753,33 +753,33 @@
         <v>CANE</v>
       </c>
       <c r="I11" t="str">
-        <v>BRESCIA</v>
+        <v>GROSSETO</v>
       </c>
       <c r="J11" t="str">
-        <v>BS</v>
+        <v>GR</v>
       </c>
       <c r="K11" t="str">
-        <v>LOMBARDIA</v>
+        <v>TOSCANA</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>84095</v>
+        <v>85197</v>
       </c>
       <c r="B12" t="str">
-        <v>FOCOLAIO CLINICO</v>
+        <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
       <c r="C12" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D12" t="str">
-        <v>18/03/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="E12" t="str">
-        <v>18/03/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="F12" t="str">
-        <v>-</v>
+        <v>19/06/2026</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -788,33 +788,33 @@
         <v>CANE</v>
       </c>
       <c r="I12" t="str">
-        <v>CINTO EUGANEO</v>
+        <v>GROSSETO</v>
       </c>
       <c r="J12" t="str">
-        <v>PD</v>
+        <v>GR</v>
       </c>
       <c r="K12" t="str">
-        <v>VENETO</v>
+        <v>TOSCANA</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>84886</v>
+        <v>85713</v>
       </c>
       <c r="B13" t="str">
         <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C13" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D13" t="str">
-        <v>25/05/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="E13" t="str">
-        <v>14/05/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="F13" t="str">
-        <v>-</v>
+        <v>21/06/2026</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -823,33 +823,33 @@
         <v>CANE</v>
       </c>
       <c r="I13" t="str">
-        <v>MALO</v>
+        <v>GAVORRANO</v>
       </c>
       <c r="J13" t="str">
-        <v>VI</v>
+        <v>GR</v>
       </c>
       <c r="K13" t="str">
-        <v>VENETO</v>
+        <v>TOSCANA</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>85485</v>
+        <v>85894</v>
       </c>
       <c r="B14" t="str">
         <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C14" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D14" t="str">
-        <v>03/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="E14" t="str">
-        <v>30/06/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="F14" t="str">
-        <v>-</v>
+        <v>28/07/2026</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -858,7 +858,7 @@
         <v>CANE</v>
       </c>
       <c r="I14" t="str">
-        <v>GROSSETO</v>
+        <v>MONTE ARGENTARIO</v>
       </c>
       <c r="J14" t="str">
         <v>GR</v>
@@ -869,22 +869,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>85013</v>
+        <v>85657</v>
       </c>
       <c r="B15" t="str">
         <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C15" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D15" t="str">
-        <v>29/05/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="E15" t="str">
-        <v>29/05/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="F15" t="str">
-        <v>-</v>
+        <v>16/07/2026</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -893,53 +893,368 @@
         <v>CANE</v>
       </c>
       <c r="I15" t="str">
-        <v>PEZZAZE</v>
+        <v>CAMPAGNATICO</v>
       </c>
       <c r="J15" t="str">
-        <v>BS</v>
+        <v>GR</v>
       </c>
       <c r="K15" t="str">
-        <v>LOMBARDIA</v>
+        <v>TOSCANA</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
+        <v>85861</v>
+      </c>
+      <c r="B16" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C16" t="str">
+        <v>E</v>
+      </c>
+      <c r="D16" t="str">
+        <v>17/06/2026</v>
+      </c>
+      <c r="E16" t="str">
+        <v>17/06/2026</v>
+      </c>
+      <c r="F16" t="str">
+        <v>17/06/2026</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>CANE</v>
+      </c>
+      <c r="I16" t="str">
+        <v>GROSSETO</v>
+      </c>
+      <c r="J16" t="str">
+        <v>GR</v>
+      </c>
+      <c r="K16" t="str">
+        <v>TOSCANA</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>85485</v>
+      </c>
+      <c r="B17" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C17" t="str">
+        <v>E</v>
+      </c>
+      <c r="D17" t="str">
+        <v>03/07/2026</v>
+      </c>
+      <c r="E17" t="str">
+        <v>30/06/2026</v>
+      </c>
+      <c r="F17" t="str">
+        <v>07/07/2026</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>CANE</v>
+      </c>
+      <c r="I17" t="str">
+        <v>GROSSETO</v>
+      </c>
+      <c r="J17" t="str">
+        <v>GR</v>
+      </c>
+      <c r="K17" t="str">
+        <v>TOSCANA</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>84096</v>
+      </c>
+      <c r="B18" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C18" t="str">
+        <v>C</v>
+      </c>
+      <c r="D18" t="str">
+        <v>27/03/2026</v>
+      </c>
+      <c r="E18" t="str">
+        <v>20/03/2026</v>
+      </c>
+      <c r="F18" t="str">
+        <v>-</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>CANE</v>
+      </c>
+      <c r="I18" t="str">
+        <v>BATTAGLIA TERME</v>
+      </c>
+      <c r="J18" t="str">
+        <v>PD</v>
+      </c>
+      <c r="K18" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>84882</v>
+      </c>
+      <c r="B19" t="str">
+        <v>POSITIVITA' DIAGNOSTICA</v>
+      </c>
+      <c r="C19" t="str">
+        <v>C</v>
+      </c>
+      <c r="D19" t="str">
+        <v>17/04/2026</v>
+      </c>
+      <c r="E19" t="str">
+        <v>15/04/2026</v>
+      </c>
+      <c r="F19" t="str">
+        <v>-</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>CANE</v>
+      </c>
+      <c r="I19" t="str">
+        <v>MALO</v>
+      </c>
+      <c r="J19" t="str">
+        <v>VI</v>
+      </c>
+      <c r="K19" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>83740</v>
+      </c>
+      <c r="B20" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C20" t="str">
+        <v>C</v>
+      </c>
+      <c r="D20" t="str">
+        <v>14/02/2026</v>
+      </c>
+      <c r="E20" t="str">
+        <v>14/02/2026</v>
+      </c>
+      <c r="F20" t="str">
+        <v>-</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>CANE</v>
+      </c>
+      <c r="I20" t="str">
+        <v>VALDOBBIADENE</v>
+      </c>
+      <c r="J20" t="str">
+        <v>TV</v>
+      </c>
+      <c r="K20" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>85011</v>
+      </c>
+      <c r="B21" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C21" t="str">
+        <v>C</v>
+      </c>
+      <c r="D21" t="str">
+        <v>15/05/2026</v>
+      </c>
+      <c r="E21" t="str">
+        <v>14/05/2026</v>
+      </c>
+      <c r="F21" t="str">
+        <v>-</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>CANE</v>
+      </c>
+      <c r="I21" t="str">
+        <v>BRESCIA</v>
+      </c>
+      <c r="J21" t="str">
+        <v>BS</v>
+      </c>
+      <c r="K21" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>84095</v>
+      </c>
+      <c r="B22" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C22" t="str">
+        <v>C</v>
+      </c>
+      <c r="D22" t="str">
+        <v>18/03/2026</v>
+      </c>
+      <c r="E22" t="str">
+        <v>18/03/2026</v>
+      </c>
+      <c r="F22" t="str">
+        <v>-</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>CANE</v>
+      </c>
+      <c r="I22" t="str">
+        <v>CINTO EUGANEO</v>
+      </c>
+      <c r="J22" t="str">
+        <v>PD</v>
+      </c>
+      <c r="K22" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>84886</v>
+      </c>
+      <c r="B23" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C23" t="str">
+        <v>C</v>
+      </c>
+      <c r="D23" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="E23" t="str">
+        <v>14/05/2026</v>
+      </c>
+      <c r="F23" t="str">
+        <v>-</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>CANE</v>
+      </c>
+      <c r="I23" t="str">
+        <v>MALO</v>
+      </c>
+      <c r="J23" t="str">
+        <v>VI</v>
+      </c>
+      <c r="K23" t="str">
+        <v>VENETO</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>85013</v>
+      </c>
+      <c r="B24" t="str">
+        <v>FOCOLAIO CLINICO</v>
+      </c>
+      <c r="C24" t="str">
+        <v>C</v>
+      </c>
+      <c r="D24" t="str">
+        <v>29/05/2026</v>
+      </c>
+      <c r="E24" t="str">
+        <v>29/05/2026</v>
+      </c>
+      <c r="F24" t="str">
+        <v>-</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>CANE</v>
+      </c>
+      <c r="I24" t="str">
+        <v>PEZZAZE</v>
+      </c>
+      <c r="J24" t="str">
+        <v>BS</v>
+      </c>
+      <c r="K24" t="str">
+        <v>LOMBARDIA</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
         <v>84885</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B25" t="str">
         <v>POSITIVITA' DIAGNOSTICA</v>
       </c>
-      <c r="C16" t="str">
+      <c r="C25" t="str">
         <v>C</v>
       </c>
-      <c r="D16" t="str">
+      <c r="D25" t="str">
         <v>20/05/2026</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E25" t="str">
         <v>01/04/2026</v>
       </c>
-      <c r="F16" t="str">
+      <c r="F25" t="str">
         <v>-</v>
       </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v>CANE</v>
-      </c>
-      <c r="I16" t="str">
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>CANE</v>
+      </c>
+      <c r="I25" t="str">
         <v>MONTE DI MALO</v>
       </c>
-      <c r="J16" t="str">
+      <c r="J25" t="str">
         <v>VI</v>
       </c>
-      <c r="K16" t="str">
+      <c r="K25" t="str">
         <v>VENETO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K25"/>
   </ignoredErrors>
 </worksheet>
 </file>